--- a/territoryARC.xlsx
+++ b/territoryARC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE83888-EFE4-4ADD-B865-44FC3E7BE9F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C0DBB2-A490-4986-AC5C-8078C9F6A0F6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="1" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="5" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
   </bookViews>
   <sheets>
     <sheet name="mun" sheetId="3" r:id="rId1"/>
@@ -19,10 +19,11 @@
     <sheet name="tech_pot" sheetId="9" r:id="rId4"/>
     <sheet name="market" sheetId="8" r:id="rId5"/>
     <sheet name="dist_market" sheetId="4" r:id="rId6"/>
-    <sheet name="Feuil4" sheetId="12" r:id="rId7"/>
+    <sheet name="dist_col" sheetId="13" r:id="rId7"/>
+    <sheet name="Feuil4" sheetId="12" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="83">
   <si>
     <t>A</t>
   </si>
@@ -108,18 +109,12 @@
     <t>AD-b</t>
   </si>
   <si>
-    <t>The technology can be installed at the site</t>
-  </si>
-  <si>
     <t>The market can not valorize the coproduct</t>
   </si>
   <si>
     <t>The market can valorize the coproduct</t>
   </si>
   <si>
-    <t>The technology can not be installed at the site</t>
-  </si>
-  <si>
     <t>lb_mark</t>
   </si>
   <si>
@@ -201,10 +196,94 @@
     <t>Other markets</t>
   </si>
   <si>
-    <t>Hypothèse</t>
-  </si>
-  <si>
-    <t>Chaque logement produit la même quantité de biodéchets</t>
+    <t>Coudun</t>
+  </si>
+  <si>
+    <t>Trosly breuil</t>
+  </si>
+  <si>
+    <t>AD-c</t>
+  </si>
+  <si>
+    <t>AD-d</t>
+  </si>
+  <si>
+    <t>AD-e</t>
+  </si>
+  <si>
+    <t>AD-f</t>
+  </si>
+  <si>
+    <t>Centralized anaerobic digestion + CHP</t>
+  </si>
+  <si>
+    <t>Centralized anaerobic digestion + CHP + composting</t>
+  </si>
+  <si>
+    <t>Centralized anaerobic digestion + upgrading</t>
+  </si>
+  <si>
+    <t>Centralized anaerobic digestion + upgrading +composting</t>
+  </si>
+  <si>
+    <t>Centralized anaerobic digestion + combustion</t>
+  </si>
+  <si>
+    <t>Centralized anaerobic digestion + combustion +composting</t>
+  </si>
+  <si>
+    <t>FERTI-NRJ</t>
+  </si>
+  <si>
+    <t>Biomet</t>
+  </si>
+  <si>
+    <t>Monchy-Humières</t>
+  </si>
+  <si>
+    <t>Antheuil-Portes</t>
+  </si>
+  <si>
+    <t>Sercges</t>
+  </si>
+  <si>
+    <t>Ressons-sur-Matz</t>
+  </si>
+  <si>
+    <t>Serches</t>
+  </si>
+  <si>
+    <t>Ferty-NRJ(Passel)</t>
+  </si>
+  <si>
+    <t>urbain</t>
+  </si>
+  <si>
+    <t>rural</t>
+  </si>
+  <si>
+    <t>Taux de tri urbain</t>
+  </si>
+  <si>
+    <t>Taux de tri rural</t>
+  </si>
+  <si>
+    <t>Produced home</t>
+  </si>
+  <si>
+    <t>Produced Building</t>
+  </si>
+  <si>
+    <t>les maisons produisent autant de biodéchets que les appartements</t>
+  </si>
+  <si>
+    <t>les citoyens produisent les mêmes qtés de biodéchets</t>
+  </si>
+  <si>
+    <t>P_trans</t>
+  </si>
+  <si>
+    <t>dist_col</t>
   </si>
 </sst>
 </file>
@@ -214,7 +293,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,13 +322,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -261,21 +359,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{00374EC6-2AEB-4CFB-BC79-47B29FA2299B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -288,6 +392,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>530225</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>154310</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>627514</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>37824</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ADEE861-E55A-4F94-BEBA-BA31DEAD2998}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8978900" y="697235"/>
+          <a:ext cx="6193289" cy="1512289"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -681,138 +834,138 @@
         <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -822,401 +975,881 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07A1C762-7C0F-4506-9633-75512DFB1A94}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+    <col min="1" max="4" width="21.81640625" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>3</v>
       </c>
       <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>mun!A2</f>
         <v>Compiègne</v>
       </c>
       <c r="B2">
-        <f>D2*[1]Communes!$H$29</f>
+        <f>E2*$B$26</f>
+        <v>317.30105497834575</v>
+      </c>
+      <c r="C2">
+        <f>F2*$B$26</f>
+        <v>919.17894502165416</v>
+      </c>
+      <c r="E2" s="6">
+        <v>755.47870232939465</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2188.5212976706052</v>
+      </c>
+      <c r="G2" s="6">
+        <v>2944</v>
+      </c>
+      <c r="I2" s="7">
+        <f>G2*[1]Communes!$H$29</f>
         <v>615.29599999999994</v>
       </c>
-      <c r="C2">
-        <f t="shared" ref="C2:C4" si="0">D2-B2</f>
+      <c r="J2" s="7">
+        <f t="shared" ref="J2:J23" si="0">G2-I2</f>
         <v>2328.7040000000002</v>
       </c>
-      <c r="D2">
+      <c r="K2" s="7">
         <v>2944</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O2" s="7"/>
+      <c r="P2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>mun!A3</f>
         <v>Venette</v>
       </c>
       <c r="B3">
-        <f>D3*[1]Communes!$U$29</f>
+        <f>E3*$B$27</f>
+        <v>103.59289408695653</v>
+      </c>
+      <c r="C3">
+        <f>F3*$B$27</f>
+        <v>39.627105913043479</v>
+      </c>
+      <c r="E3" s="6">
+        <v>134.53622608695653</v>
+      </c>
+      <c r="F3" s="6">
+        <v>51.463773913043475</v>
+      </c>
+      <c r="G3" s="6">
+        <v>186</v>
+      </c>
+      <c r="I3" s="7">
+        <f>G3*[1]Communes!$U$29</f>
         <v>124.80600000000001</v>
       </c>
-      <c r="C3">
+      <c r="J3" s="7">
         <f t="shared" si="0"/>
         <v>61.193999999999988</v>
       </c>
-      <c r="D3">
+      <c r="K3" s="7">
         <v>186</v>
       </c>
-      <c r="I3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>mun!A4</f>
         <v>Jaux</v>
       </c>
       <c r="B4">
-        <f>D4*[1]Communes!$J$29</f>
+        <f t="shared" ref="B4:B23" si="1">E4*$B$27</f>
+        <v>120.88273482352942</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C23" si="2">F4*$B$27</f>
+        <v>22.337265176470591</v>
+      </c>
+      <c r="E4" s="6">
+        <v>156.99056470588235</v>
+      </c>
+      <c r="F4" s="6">
+        <v>29.009435294117651</v>
+      </c>
+      <c r="G4" s="6">
+        <v>186</v>
+      </c>
+      <c r="I4" s="7">
+        <f>G4*[1]Communes!$J$29</f>
         <v>147.49800000000002</v>
       </c>
-      <c r="C4">
+      <c r="J4" s="7">
         <f t="shared" si="0"/>
         <v>38.501999999999981</v>
       </c>
-      <c r="D4">
+      <c r="K4" s="7">
         <v>186</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M4" t="s">
+        <v>74</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>mun!A5</f>
         <v>Armancourt</v>
       </c>
       <c r="B5">
-        <f>D5*[1]Communes!$B$29</f>
+        <f t="shared" si="1"/>
+        <v>33.750946347048298</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="2"/>
+        <v>3.2090536529516989</v>
+      </c>
+      <c r="E5" s="6">
+        <v>43.83239785330948</v>
+      </c>
+      <c r="F5" s="6">
+        <v>4.167602146690518</v>
+      </c>
+      <c r="G5" s="6">
+        <v>48</v>
+      </c>
+      <c r="I5" s="7">
+        <f>G5*[1]Communes!$B$29</f>
         <v>42.864000000000004</v>
       </c>
-      <c r="C5">
-        <f>D5-B5</f>
+      <c r="J5" s="7">
+        <f t="shared" si="0"/>
         <v>5.1359999999999957</v>
       </c>
-      <c r="D5">
+      <c r="K5" s="7">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>mun!A6</f>
         <v>Le Meux</v>
       </c>
       <c r="B6">
-        <f>D6*[1]Communes!$O$29</f>
+        <f t="shared" si="1"/>
+        <v>87.710726398155884</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="2"/>
+        <v>13.159273601844097</v>
+      </c>
+      <c r="E6" s="6">
+        <v>113.91003428331933</v>
+      </c>
+      <c r="F6" s="6">
+        <v>17.089965716680645</v>
+      </c>
+      <c r="G6" s="6">
+        <v>131</v>
+      </c>
+      <c r="I6" s="7">
+        <f>G6*[1]Communes!$O$29</f>
         <v>107.81299999999999</v>
       </c>
-      <c r="C6">
-        <f t="shared" ref="C6:C23" si="1">D6-B6</f>
+      <c r="J6" s="7">
+        <f t="shared" si="0"/>
         <v>23.187000000000012</v>
       </c>
-      <c r="D6">
+      <c r="K6" s="7">
         <v>131</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>mun!A7</f>
         <v>La Croix-St-Ouen</v>
       </c>
       <c r="B7">
-        <f>D7*[1]Communes!$M$29</f>
+        <f t="shared" si="1"/>
+        <v>52.974105983943609</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="2"/>
+        <v>16.325894016056395</v>
+      </c>
+      <c r="E7" s="6">
+        <v>68.797540238887805</v>
+      </c>
+      <c r="F7" s="6">
+        <v>21.202459761112202</v>
+      </c>
+      <c r="G7" s="6">
+        <v>90</v>
+      </c>
+      <c r="I7" s="7">
+        <f>G7*[1]Communes!$M$29</f>
         <v>65.069999999999993</v>
       </c>
-      <c r="C7">
-        <f t="shared" si="1"/>
+      <c r="J7" s="7">
+        <f t="shared" si="0"/>
         <v>24.930000000000007</v>
       </c>
-      <c r="D7">
+      <c r="K7" s="7">
         <v>90</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>mun!A8</f>
         <v>St-Sauveur</v>
       </c>
       <c r="B8">
-        <f>D8*[1]Communes!$S$29</f>
+        <f t="shared" si="1"/>
+        <v>111.8313283800905</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="2"/>
+        <v>2.8986716199095062</v>
+      </c>
+      <c r="E8" s="6">
+        <v>145.23549140271493</v>
+      </c>
+      <c r="F8" s="6">
+        <v>3.7645085972850727</v>
+      </c>
+      <c r="G8" s="6">
+        <v>149</v>
+      </c>
+      <c r="I8" s="7">
+        <f>G8*[1]Communes!$S$29</f>
         <v>144.083</v>
       </c>
-      <c r="C8">
-        <f t="shared" si="1"/>
+      <c r="J8" s="7">
+        <f t="shared" si="0"/>
         <v>4.9170000000000016</v>
       </c>
-      <c r="D8">
+      <c r="K8" s="7">
         <v>149</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>mun!A9</f>
         <v>Bethisy-St-Pierre</v>
       </c>
       <c r="B9">
-        <f>D9*[1]Communes!$D$29</f>
+        <f t="shared" si="1"/>
+        <v>97.424969678873225</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="2"/>
+        <v>34.245030321126777</v>
+      </c>
+      <c r="E9" s="6">
+        <v>126.52593464788731</v>
+      </c>
+      <c r="F9" s="6">
+        <v>44.474065352112696</v>
+      </c>
+      <c r="G9" s="6">
+        <v>171</v>
+      </c>
+      <c r="I9" s="7">
+        <f>G9*[1]Communes!$D$29</f>
         <v>118.16099999999999</v>
       </c>
-      <c r="C9">
-        <f t="shared" si="1"/>
+      <c r="J9" s="7">
+        <f t="shared" si="0"/>
         <v>52.839000000000013</v>
       </c>
-      <c r="D9">
+      <c r="K9" s="7">
         <v>171</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>mun!A10</f>
         <v>Bethisy-St-Martin</v>
       </c>
       <c r="B10">
-        <f>D10*[1]Communes!$C$29</f>
+        <f t="shared" si="1"/>
+        <v>36.245639685658155</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="2"/>
+        <v>2.254360314341846</v>
+      </c>
+      <c r="E10" s="6">
+        <v>47.072259332023577</v>
+      </c>
+      <c r="F10" s="6">
+        <v>2.9277406679764231</v>
+      </c>
+      <c r="G10" s="6">
+        <v>50</v>
+      </c>
+      <c r="I10" s="7">
+        <f>G10*[1]Communes!$C$29</f>
         <v>46.6</v>
       </c>
-      <c r="C10">
-        <f t="shared" si="1"/>
+      <c r="J10" s="7">
+        <f t="shared" si="0"/>
         <v>3.3999999999999986</v>
       </c>
-      <c r="D10">
+      <c r="K10" s="7">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>mun!A11</f>
         <v>Bienville</v>
       </c>
       <c r="B11">
-        <f>D11*[1]Communes!$E$29</f>
+        <f t="shared" si="1"/>
+        <v>22.379279999999998</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="2"/>
+        <v>0.7207200000000008</v>
+      </c>
+      <c r="E11" s="6">
+        <v>29.063999999999997</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.93600000000000105</v>
+      </c>
+      <c r="G11" s="6">
+        <v>30</v>
+      </c>
+      <c r="I11" s="7">
+        <f>G11*[1]Communes!$E$29</f>
         <v>28.68</v>
       </c>
-      <c r="C11">
-        <f t="shared" si="1"/>
+      <c r="J11" s="7">
+        <f t="shared" si="0"/>
         <v>1.3200000000000003</v>
       </c>
-      <c r="D11">
+      <c r="K11" s="7">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>mun!A12</f>
         <v>Choisy-au-Bac</v>
       </c>
       <c r="B12">
-        <f>D12*[1]Communes!$F$29</f>
+        <f t="shared" si="1"/>
+        <v>138.05210076787807</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="2"/>
+        <v>25.957899232121925</v>
+      </c>
+      <c r="E12" s="6">
+        <v>179.2884425556858</v>
+      </c>
+      <c r="F12" s="6">
+        <v>33.711557444314188</v>
+      </c>
+      <c r="G12" s="6">
+        <v>213</v>
+      </c>
+      <c r="I12" s="7">
+        <f>G12*[1]Communes!$F$29</f>
         <v>172.53</v>
       </c>
-      <c r="C12">
-        <f t="shared" si="1"/>
+      <c r="J12" s="7">
+        <f t="shared" si="0"/>
         <v>40.47</v>
       </c>
-      <c r="D12">
+      <c r="K12" s="7">
         <v>213</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>mun!A13</f>
         <v>Clairoix</v>
       </c>
       <c r="B13">
-        <f>D13*[1]Communes!$G$29</f>
+        <f t="shared" si="1"/>
+        <v>73.2398007460733</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="2"/>
+        <v>10.690199253926705</v>
+      </c>
+      <c r="E13" s="6">
+        <v>95.116624345549738</v>
+      </c>
+      <c r="F13" s="6">
+        <v>13.883375654450266</v>
+      </c>
+      <c r="G13" s="6">
+        <v>109</v>
+      </c>
+      <c r="I13" s="7">
+        <f>G13*[1]Communes!$G$29</f>
         <v>91.23299999999999</v>
       </c>
-      <c r="C13">
-        <f t="shared" si="1"/>
+      <c r="J13" s="7">
+        <f t="shared" si="0"/>
         <v>17.76700000000001</v>
       </c>
-      <c r="D13">
+      <c r="K13" s="7">
         <v>109</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>mun!A14</f>
         <v>Janville</v>
       </c>
       <c r="B14">
-        <f>D14*[1]Communes!$I$29</f>
+        <f t="shared" si="1"/>
+        <v>29.195244054794522</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="2"/>
+        <v>2.3747559452054809</v>
+      </c>
+      <c r="E14" s="6">
+        <v>37.915901369863015</v>
+      </c>
+      <c r="F14" s="6">
+        <v>3.0840986301369884</v>
+      </c>
+      <c r="G14" s="6">
+        <v>41</v>
+      </c>
+      <c r="I14" s="7">
+        <f>G14*[1]Communes!$I$29</f>
         <v>37.064</v>
       </c>
-      <c r="C14">
-        <f t="shared" si="1"/>
+      <c r="J14" s="7">
+        <f t="shared" si="0"/>
         <v>3.9359999999999999</v>
       </c>
-      <c r="D14">
+      <c r="K14" s="7">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>mun!A15</f>
         <v>Jonquières</v>
       </c>
       <c r="B15">
-        <f>D15*[1]Communes!$K$29</f>
+        <f t="shared" si="1"/>
+        <v>30.638913768115941</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="2"/>
+        <v>0.93108623188405915</v>
+      </c>
+      <c r="E15" s="6">
+        <v>39.790797101449272</v>
+      </c>
+      <c r="F15" s="6">
+        <v>1.2092028985507262</v>
+      </c>
+      <c r="G15" s="6">
+        <v>41</v>
+      </c>
+      <c r="I15" s="7">
+        <f>G15*[1]Communes!$K$29</f>
         <v>39.482999999999997</v>
       </c>
-      <c r="C15">
-        <f t="shared" si="1"/>
+      <c r="J15" s="7">
+        <f t="shared" si="0"/>
         <v>1.517000000000003</v>
       </c>
-      <c r="D15">
+      <c r="K15" s="7">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="M15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>mun!A16</f>
         <v>Lachelle</v>
       </c>
       <c r="B16">
-        <f>D16*[1]Communes!$L$29</f>
+        <f t="shared" si="1"/>
+        <v>30.888256593516207</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="2"/>
+        <v>1.4517434064837931</v>
+      </c>
+      <c r="E16" s="6">
+        <v>40.11461895261845</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1.8853810473815493</v>
+      </c>
+      <c r="G16" s="6">
+        <v>42</v>
+      </c>
+      <c r="I16" s="7">
+        <f>G16*[1]Communes!$L$29</f>
         <v>39.521999999999998</v>
       </c>
-      <c r="C16">
-        <f t="shared" si="1"/>
+      <c r="J16" s="7">
+        <f t="shared" si="0"/>
         <v>2.4780000000000015</v>
       </c>
-      <c r="D16">
+      <c r="K16" s="7">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="M16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>mun!A17</f>
         <v>Margny-lès-Compiègne</v>
       </c>
       <c r="B17">
-        <f>D17*[1]Communes!$N$29</f>
+        <f>E17*$B$26</f>
+        <v>111.01133208510636</v>
+      </c>
+      <c r="C17">
+        <f>F17*$B$26</f>
+        <v>114.94866791489363</v>
+      </c>
+      <c r="E17" s="6">
+        <v>264.31269544072944</v>
+      </c>
+      <c r="F17" s="6">
+        <v>273.68730455927056</v>
+      </c>
+      <c r="G17" s="6">
+        <v>538</v>
+      </c>
+      <c r="I17" s="7">
+        <f>G17*[1]Communes!$N$29</f>
         <v>241.024</v>
       </c>
-      <c r="C17">
-        <f t="shared" si="1"/>
+      <c r="J17" s="7">
+        <f t="shared" si="0"/>
         <v>296.976</v>
       </c>
-      <c r="D17">
+      <c r="K17" s="7">
         <v>538</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="M17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>mun!A18</f>
         <v>Nery</v>
       </c>
+      <c r="B18">
+        <f t="shared" si="1"/>
+        <v>23.820655157894738</v>
+      </c>
       <c r="C18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>0.81934484210526481</v>
+      </c>
+      <c r="E18" s="6">
+        <v>30.935915789473682</v>
+      </c>
+      <c r="F18" s="6">
+        <v>1.064084210526318</v>
+      </c>
+      <c r="G18" s="6">
         <v>32</v>
       </c>
-      <c r="D18">
+      <c r="I18" s="7"/>
+      <c r="J18" s="7">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="K18" s="7">
+        <v>32</v>
+      </c>
+      <c r="M18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>mun!A19</f>
         <v>Saint-Jean-aux-Bois</v>
       </c>
       <c r="B19">
-        <f>D19*[1]Communes!$R$29</f>
+        <f t="shared" si="1"/>
+        <v>14.662614999999997</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="2"/>
+        <v>0.73738500000000151</v>
+      </c>
+      <c r="E19" s="6">
+        <v>19.042357142857139</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.95764285714285902</v>
+      </c>
+      <c r="G19" s="6">
+        <v>20</v>
+      </c>
+      <c r="I19" s="7">
+        <f>G19*[1]Communes!$R$29</f>
         <v>19.18</v>
       </c>
-      <c r="C19">
-        <f t="shared" si="1"/>
+      <c r="J19" s="7">
+        <f t="shared" si="0"/>
         <v>0.82000000000000028</v>
       </c>
-      <c r="D19">
+      <c r="K19" s="7">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="M19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>mun!A20</f>
         <v>Saintines</v>
       </c>
       <c r="B20">
-        <f>D20*[1]Communes!$Q$29</f>
+        <f t="shared" si="1"/>
+        <v>37.973147649862518</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="2"/>
+        <v>2.8368523501374874</v>
+      </c>
+      <c r="E20" s="6">
+        <v>49.315776168652619</v>
+      </c>
+      <c r="F20" s="6">
+        <v>3.6842238313473863</v>
+      </c>
+      <c r="G20" s="6">
+        <v>53</v>
+      </c>
+      <c r="I20" s="7">
+        <f>G20*[1]Communes!$Q$29</f>
         <v>48.177</v>
       </c>
-      <c r="C20">
-        <f t="shared" si="1"/>
+      <c r="J20" s="7">
+        <f t="shared" si="0"/>
         <v>4.8230000000000004</v>
       </c>
-      <c r="D20">
+      <c r="K20" s="7">
         <v>53</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="M20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>mun!A21</f>
         <v>Saint-Vaast de Longmont</v>
       </c>
       <c r="B21">
-        <f>D21*[1]Communes!$T$29</f>
+        <f t="shared" si="1"/>
+        <v>23.87</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="6">
         <v>31</v>
       </c>
-      <c r="C21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D21">
+      <c r="F21" s="6">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I21" s="7">
+        <f>G21*[1]Communes!$T$29</f>
+        <v>31</v>
+      </c>
+      <c r="J21" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="7">
+        <v>31</v>
+      </c>
+      <c r="M21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>mun!A22</f>
         <v>Verberie</v>
       </c>
       <c r="B22">
-        <f>D22*[1]Communes!$V$29</f>
+        <f t="shared" si="1"/>
+        <v>95.373320327954175</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="2"/>
+        <v>50.926679672045815</v>
+      </c>
+      <c r="E22" s="6">
+        <v>123.86145497136906</v>
+      </c>
+      <c r="F22" s="6">
+        <v>66.138545028630929</v>
+      </c>
+      <c r="G22" s="6">
+        <v>190</v>
+      </c>
+      <c r="I22" s="7">
+        <f>G22*[1]Communes!$V$29</f>
         <v>114.95</v>
       </c>
-      <c r="C22">
-        <f t="shared" si="1"/>
+      <c r="J22" s="7">
+        <f t="shared" si="0"/>
         <v>75.05</v>
       </c>
-      <c r="D22">
+      <c r="K22" s="7">
         <v>190</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="M22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>mun!A23</f>
         <v>Vieux-Moulin</v>
       </c>
       <c r="B23">
-        <f>D23*[1]Communes!$W$29</f>
+        <f t="shared" si="1"/>
+        <v>38.794102415213949</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="2"/>
+        <v>1.2458975847860556</v>
+      </c>
+      <c r="E23" s="6">
+        <v>50.381951188589539</v>
+      </c>
+      <c r="F23" s="6">
+        <v>1.6180488114104619</v>
+      </c>
+      <c r="G23" s="6">
+        <v>52</v>
+      </c>
+      <c r="I23" s="7">
+        <f>G23*[1]Communes!$W$29</f>
         <v>50.128</v>
       </c>
-      <c r="C23">
-        <f t="shared" si="1"/>
+      <c r="J23" s="7">
+        <f t="shared" si="0"/>
         <v>1.8719999999999999</v>
       </c>
-      <c r="D23">
+      <c r="K23" s="7">
         <v>52</v>
+      </c>
+      <c r="M23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="5">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="5">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="B17:C17" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1232,15 +1865,15 @@
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B1" t="str">
         <f>INDEX(mun!$B:$B,COLUMN(A1)+1)</f>
-        <v>X</v>
+        <v>Coudun</v>
       </c>
       <c r="C1" t="str">
         <f>INDEX(mun!$B:$B,COLUMN(B1)+1)</f>
-        <v>Y</v>
-      </c>
-      <c r="D1" t="str">
+        <v>Trosly breuil</v>
+      </c>
+      <c r="D1">
         <f>INDEX(mun!$B:$B,COLUMN(C1)+1)</f>
-        <v>Z</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
@@ -1385,13 +2018,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DCAE16-4335-49F9-8C26-3341265BB48C}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>19</v>
       </c>
@@ -1407,14 +2040,26 @@
       <c r="F1" t="s">
         <v>23</v>
       </c>
-      <c r="J1">
-        <v>1</v>
-      </c>
-      <c r="K1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>mun!A2</f>
         <v>Compiègne</v>
@@ -1434,14 +2079,26 @@
       <c r="F2">
         <v>0</v>
       </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>mun!A3</f>
         <v>Venette</v>
@@ -1461,8 +2118,26 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>mun!A4</f>
         <v>Jaux</v>
@@ -1482,8 +2157,26 @@
       <c r="F4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>mun!A5</f>
         <v>Armancourt</v>
@@ -1503,8 +2196,26 @@
       <c r="F5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f>mun!A6</f>
         <v>Le Meux</v>
@@ -1524,8 +2235,26 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f>mun!A7</f>
         <v>La Croix-St-Ouen</v>
@@ -1545,8 +2274,20 @@
       <c r="F7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f>mun!A8</f>
         <v>St-Sauveur</v>
@@ -1566,8 +2307,20 @@
       <c r="F8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>mun!A9</f>
         <v>Bethisy-St-Pierre</v>
@@ -1587,8 +2340,20 @@
       <c r="F9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>mun!A10</f>
         <v>Bethisy-St-Martin</v>
@@ -1608,8 +2373,20 @@
       <c r="F10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>mun!A11</f>
         <v>Bienville</v>
@@ -1629,8 +2406,20 @@
       <c r="F11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>mun!A12</f>
         <v>Choisy-au-Bac</v>
@@ -1650,8 +2439,20 @@
       <c r="F12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>mun!A13</f>
         <v>Clairoix</v>
@@ -1671,8 +2472,20 @@
       <c r="F13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>mun!A14</f>
         <v>Janville</v>
@@ -1692,8 +2505,20 @@
       <c r="F14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>mun!A15</f>
         <v>Jonquières</v>
@@ -1713,8 +2538,20 @@
       <c r="F15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>mun!A16</f>
         <v>Lachelle</v>
@@ -1734,12 +2571,20 @@
       <c r="F16">
         <v>0</v>
       </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
       <c r="J16">
-        <f>11*20*12</f>
-        <v>2640</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>mun!A17</f>
         <v>Margny-lès-Compiègne</v>
@@ -1759,8 +2604,20 @@
       <c r="F17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>mun!A18</f>
         <v>Nery</v>
@@ -1780,8 +2637,20 @@
       <c r="F18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>mun!A19</f>
         <v>Saint-Jean-aux-Bois</v>
@@ -1801,8 +2670,20 @@
       <c r="F19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>mun!A20</f>
         <v>Saintines</v>
@@ -1822,8 +2703,20 @@
       <c r="F20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>mun!A21</f>
         <v>Saint-Vaast de Longmont</v>
@@ -1843,8 +2736,20 @@
       <c r="F21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>mun!A22</f>
         <v>Verberie</v>
@@ -1864,8 +2769,20 @@
       <c r="F22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>mun!A23</f>
         <v>Vieux-Moulin</v>
@@ -1885,11 +2802,22 @@
       <c r="F23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" t="str">
-        <f>mun!B2</f>
-        <v>X</v>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>65</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1898,19 +2826,30 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" t="str">
-        <f>mun!B3</f>
-        <v>Y</v>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>67</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1922,31 +2861,22 @@
         <v>1</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" t="str">
-        <f>mun!B4</f>
-        <v>Z</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1956,9 +2886,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C462B02-F830-4504-8CFB-862612762922}">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="20.08984375" customWidth="1"/>
     <col min="10" max="10" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1978,11 +2909,14 @@
       <c r="E1" t="s">
         <v>15</v>
       </c>
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
       <c r="I1">
         <v>1</v>
       </c>
       <c r="J1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -1997,16 +2931,19 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -2026,6 +2963,9 @@
       <c r="E3">
         <v>0</v>
       </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
@@ -2036,13 +2976,16 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
@@ -2057,9 +3000,12 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>0</v>
       </c>
     </row>
@@ -2072,12 +3018,15 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>0</v>
       </c>
     </row>
@@ -2090,13 +3039,16 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -2108,13 +3060,16 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
       </c>
       <c r="J8" s="2"/>
     </row>
@@ -2127,12 +3082,15 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>0</v>
       </c>
       <c r="J9" s="2"/>
@@ -2146,13 +3104,16 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
       </c>
       <c r="J10" s="2"/>
     </row>
@@ -2164,6 +3125,18 @@
       <c r="B11">
         <v>1</v>
       </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
@@ -2173,6 +3146,18 @@
       <c r="B12">
         <v>1</v>
       </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
@@ -2182,6 +3167,18 @@
       <c r="B13">
         <v>1</v>
       </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
@@ -2191,6 +3188,18 @@
       <c r="B14">
         <v>1</v>
       </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
@@ -2200,6 +3209,18 @@
       <c r="B15">
         <v>1</v>
       </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
@@ -2209,8 +3230,20 @@
       <c r="B16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>tech_pot!A17</f>
         <v>Margny-lès-Compiègne</v>
@@ -2218,8 +3251,20 @@
       <c r="B17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>tech_pot!A18</f>
         <v>Nery</v>
@@ -2227,8 +3272,20 @@
       <c r="B18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>tech_pot!A19</f>
         <v>Saint-Jean-aux-Bois</v>
@@ -2236,8 +3293,20 @@
       <c r="B19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>tech_pot!A20</f>
         <v>Saintines</v>
@@ -2245,8 +3314,20 @@
       <c r="B20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>tech_pot!A21</f>
         <v>Saint-Vaast de Longmont</v>
@@ -2254,8 +3335,20 @@
       <c r="B21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>tech_pot!A22</f>
         <v>Verberie</v>
@@ -2263,8 +3356,20 @@
       <c r="B22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>tech_pot!A23</f>
         <v>Vieux-Moulin</v>
@@ -2272,59 +3377,117 @@
       <c r="B23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="str">
-        <f>tech_pot!A24</f>
-        <v>X</v>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>72</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="str">
-        <f>tech_pot!A25</f>
-        <v>Y</v>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>67</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="str">
-        <f>tech_pot!A26</f>
-        <v>Z</v>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>68</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="str">
-        <f>mun!C2</f>
-        <v>E</v>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>71</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="str">
-        <f>mun!C3</f>
-        <v>F</v>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>70</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="str">
-        <f>mun!C4</f>
-        <v>G</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2334,127 +3497,100 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08958C74-E6C0-46D4-987A-6DEF0A0AB368}">
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.81640625" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(A1)+1)</f>
-        <v>Compiègne</v>
-      </c>
-      <c r="C1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(B1)+1)</f>
-        <v>Venette</v>
-      </c>
-      <c r="D1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(C1)+1)</f>
-        <v>Jaux</v>
-      </c>
-      <c r="E1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(D1)+1)</f>
-        <v>Armancourt</v>
-      </c>
-      <c r="F1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(E1)+1)</f>
-        <v>Le Meux</v>
-      </c>
-      <c r="G1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(F1)+1)</f>
-        <v>La Croix-St-Ouen</v>
-      </c>
-      <c r="H1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(G1)+1)</f>
-        <v>St-Sauveur</v>
-      </c>
-      <c r="I1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(H1)+1)</f>
-        <v>Bethisy-St-Pierre</v>
-      </c>
-      <c r="J1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(I1)+1)</f>
-        <v>Bethisy-St-Martin</v>
-      </c>
-      <c r="K1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(J1)+1)</f>
-        <v>Bienville</v>
-      </c>
-      <c r="L1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(K1)+1)</f>
-        <v>Choisy-au-Bac</v>
-      </c>
-      <c r="M1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(L1)+1)</f>
-        <v>Clairoix</v>
-      </c>
-      <c r="N1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(M1)+1)</f>
-        <v>Janville</v>
-      </c>
-      <c r="O1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(N1)+1)</f>
-        <v>Jonquières</v>
-      </c>
-      <c r="P1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(O1)+1)</f>
-        <v>Lachelle</v>
-      </c>
-      <c r="Q1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(P1)+1)</f>
-        <v>Margny-lès-Compiègne</v>
-      </c>
-      <c r="R1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(Q1)+1)</f>
-        <v>Nery</v>
-      </c>
-      <c r="S1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(R1)+1)</f>
-        <v>Saint-Jean-aux-Bois</v>
-      </c>
-      <c r="T1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(S1)+1)</f>
-        <v>Saintines</v>
-      </c>
-      <c r="U1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(T1)+1)</f>
-        <v>Saint-Vaast de Longmont</v>
-      </c>
-      <c r="V1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(U1)+1)</f>
-        <v>Verberie</v>
-      </c>
-      <c r="W1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(V1)+1)</f>
-        <v>Vieux-Moulin</v>
-      </c>
-      <c r="X1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(W1)+1)</f>
-        <v>X</v>
-      </c>
-      <c r="Y1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(X1)+1)</f>
-        <v>Y</v>
-      </c>
-      <c r="Z1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(Y1)+1)</f>
-        <v>Z</v>
-      </c>
-      <c r="AA1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(Z1)+1)</f>
-        <v>E</v>
-      </c>
-      <c r="AB1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(AA1)+1)</f>
-        <v>F</v>
-      </c>
-      <c r="AC1" t="str">
-        <f>INDEX(market!$A:$A,COLUMN(AB1)+1)</f>
-        <v>G</v>
+      <c r="B1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>43</v>
+      </c>
+      <c r="R1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S1" t="s">
+        <v>45</v>
+      </c>
+      <c r="T1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U1" t="s">
+        <v>47</v>
+      </c>
+      <c r="V1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.35">
@@ -2462,32 +3598,89 @@
         <f>tech_pot!A2</f>
         <v>Compiègne</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="4">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>30</v>
+      <c r="C2" s="4">
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>13</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
+      </c>
+      <c r="I2">
+        <v>14</v>
+      </c>
+      <c r="J2">
+        <v>21</v>
+      </c>
+      <c r="K2">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2">
+      <c r="L2">
         <v>5</v>
       </c>
-      <c r="H2">
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="N2">
+        <v>4</v>
+      </c>
+      <c r="O2">
+        <v>6</v>
+      </c>
+      <c r="P2">
+        <v>10</v>
+      </c>
+      <c r="Q2">
+        <v>10</v>
+      </c>
+      <c r="R2">
+        <v>2</v>
+      </c>
+      <c r="S2">
+        <v>20</v>
+      </c>
+      <c r="T2">
+        <v>10</v>
+      </c>
+      <c r="U2">
+        <v>16</v>
+      </c>
+      <c r="V2">
+        <v>18</v>
+      </c>
+      <c r="W2">
+        <v>16</v>
+      </c>
+      <c r="X2">
+        <v>9</v>
+      </c>
+      <c r="Y2">
+        <v>28</v>
+      </c>
+      <c r="Z2">
+        <v>10</v>
+      </c>
+      <c r="AA2">
+        <v>12</v>
+      </c>
+      <c r="AB2">
         <v>50</v>
       </c>
-      <c r="I2">
-        <v>60</v>
-      </c>
-      <c r="J2">
-        <v>20</v>
+      <c r="AC2">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.35">
@@ -2496,31 +3689,88 @@
         <v>Venette</v>
       </c>
       <c r="B3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J3">
-        <v>44</v>
+        <v>17</v>
+      </c>
+      <c r="K3">
+        <v>18</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>9</v>
+      </c>
+      <c r="N3">
+        <v>7</v>
+      </c>
+      <c r="O3">
+        <v>9</v>
+      </c>
+      <c r="P3">
+        <v>9</v>
+      </c>
+      <c r="Q3">
+        <v>6</v>
+      </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
+      <c r="S3">
+        <v>19</v>
+      </c>
+      <c r="T3">
+        <v>17</v>
+      </c>
+      <c r="U3">
+        <v>15</v>
+      </c>
+      <c r="V3">
+        <v>17</v>
+      </c>
+      <c r="W3">
+        <v>18</v>
+      </c>
+      <c r="X3">
+        <v>17</v>
+      </c>
+      <c r="Y3">
+        <v>27</v>
+      </c>
+      <c r="Z3">
+        <v>9</v>
+      </c>
+      <c r="AA3">
+        <v>12</v>
+      </c>
+      <c r="AB3">
+        <v>54</v>
+      </c>
+      <c r="AC3">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.35">
@@ -2529,31 +3779,88 @@
         <v>Jaux</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
-      <c r="E4">
-        <v>40</v>
-      </c>
       <c r="F4">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="J4">
-        <v>96</v>
+        <v>15</v>
+      </c>
+      <c r="K4">
+        <v>17</v>
+      </c>
+      <c r="L4">
+        <v>13</v>
+      </c>
+      <c r="M4">
+        <v>13</v>
+      </c>
+      <c r="N4">
+        <v>11</v>
+      </c>
+      <c r="O4">
+        <v>13</v>
+      </c>
+      <c r="P4">
+        <v>6</v>
+      </c>
+      <c r="Q4">
+        <v>8</v>
+      </c>
+      <c r="R4">
+        <v>7</v>
+      </c>
+      <c r="S4">
+        <v>17</v>
+      </c>
+      <c r="T4">
+        <v>17</v>
+      </c>
+      <c r="U4">
+        <v>14</v>
+      </c>
+      <c r="V4">
+        <v>14</v>
+      </c>
+      <c r="W4">
+        <v>12</v>
+      </c>
+      <c r="X4">
+        <v>15</v>
+      </c>
+      <c r="Y4">
+        <v>30</v>
+      </c>
+      <c r="Z4">
+        <v>13</v>
+      </c>
+      <c r="AA4">
+        <v>15</v>
+      </c>
+      <c r="AB4">
+        <v>58</v>
+      </c>
+      <c r="AC4">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.35">
@@ -2562,31 +3869,88 @@
         <v>Armancourt</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
         <v>10</v>
       </c>
-      <c r="D5">
-        <v>40</v>
-      </c>
-      <c r="E5">
+      <c r="J5">
+        <v>13</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>16</v>
+      </c>
+      <c r="M5">
+        <v>16</v>
+      </c>
+      <c r="N5">
+        <v>13</v>
+      </c>
+      <c r="O5">
+        <v>16</v>
+      </c>
+      <c r="P5">
         <v>5</v>
       </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
+      <c r="Q5">
+        <v>10</v>
+      </c>
+      <c r="R5">
+        <v>9</v>
+      </c>
+      <c r="S5">
+        <v>15</v>
+      </c>
+      <c r="T5">
+        <v>16</v>
+      </c>
+      <c r="U5">
+        <v>12</v>
+      </c>
+      <c r="V5">
+        <v>12</v>
+      </c>
+      <c r="W5">
+        <v>10</v>
+      </c>
+      <c r="X5">
+        <v>17</v>
+      </c>
+      <c r="Y5">
+        <v>33</v>
+      </c>
+      <c r="Z5">
+        <v>14</v>
+      </c>
+      <c r="AA5">
+        <v>17</v>
+      </c>
+      <c r="AB5">
+        <v>60</v>
+      </c>
+      <c r="AC5">
         <v>30</v>
-      </c>
-      <c r="H5">
-        <v>74</v>
-      </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.35">
@@ -2595,31 +3959,88 @@
         <v>Le Meux</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
+      </c>
+      <c r="J6">
+        <v>13</v>
+      </c>
+      <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>16</v>
+      </c>
+      <c r="M6">
+        <v>16</v>
+      </c>
+      <c r="N6">
+        <v>14</v>
+      </c>
+      <c r="O6">
+        <v>16</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <v>10</v>
+      </c>
+      <c r="R6">
+        <v>11</v>
+      </c>
+      <c r="S6">
+        <v>14</v>
+      </c>
+      <c r="T6">
+        <v>16</v>
+      </c>
+      <c r="U6">
+        <v>11</v>
+      </c>
+      <c r="V6">
+        <v>13</v>
+      </c>
+      <c r="W6">
+        <v>11</v>
+      </c>
+      <c r="X6">
+        <v>24</v>
+      </c>
+      <c r="Y6">
+        <v>34</v>
+      </c>
+      <c r="Z6">
+        <v>14</v>
+      </c>
+      <c r="AA6">
         <v>20</v>
       </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>50</v>
-      </c>
-      <c r="H6">
-        <v>20</v>
-      </c>
-      <c r="I6">
-        <v>25</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
+      <c r="AB6">
+        <v>62</v>
+      </c>
+      <c r="AC6">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.35">
@@ -2628,31 +4049,88 @@
         <v>La Croix-St-Ouen</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>17</v>
+      </c>
+      <c r="M7">
+        <v>15</v>
+      </c>
+      <c r="N7">
+        <v>15</v>
+      </c>
+      <c r="O7">
+        <v>17</v>
+      </c>
+      <c r="P7">
+        <v>8</v>
+      </c>
+      <c r="Q7">
+        <v>14</v>
+      </c>
+      <c r="R7">
+        <v>11</v>
+      </c>
+      <c r="S7">
+        <v>10</v>
+      </c>
+      <c r="T7">
+        <v>9</v>
+      </c>
+      <c r="U7">
+        <v>7</v>
+      </c>
+      <c r="V7">
+        <v>8</v>
+      </c>
+      <c r="W7">
+        <v>7</v>
+      </c>
+      <c r="X7">
+        <v>16</v>
+      </c>
+      <c r="Y7">
         <v>35</v>
       </c>
-      <c r="J7">
-        <v>96</v>
+      <c r="Z7">
+        <v>18</v>
+      </c>
+      <c r="AA7">
+        <v>20</v>
+      </c>
+      <c r="AB7">
+        <v>64</v>
+      </c>
+      <c r="AC7">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.35">
@@ -2660,113 +4138,1884 @@
         <f>tech_pot!A8</f>
         <v>St-Sauveur</v>
       </c>
+      <c r="B8">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
+      </c>
+      <c r="L8">
+        <v>22</v>
+      </c>
+      <c r="M8">
+        <v>26</v>
+      </c>
+      <c r="N8">
+        <v>20</v>
+      </c>
+      <c r="O8">
+        <v>21</v>
+      </c>
+      <c r="P8">
+        <v>12</v>
+      </c>
+      <c r="Q8">
+        <v>18</v>
+      </c>
+      <c r="R8">
+        <v>16</v>
+      </c>
+      <c r="S8">
+        <v>5</v>
+      </c>
+      <c r="T8">
+        <v>14</v>
+      </c>
+      <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>4</v>
+      </c>
+      <c r="W8">
+        <v>5</v>
+      </c>
+      <c r="X8">
+        <v>20</v>
+      </c>
+      <c r="Y8">
+        <v>39</v>
+      </c>
+      <c r="Z8">
+        <v>22</v>
+      </c>
+      <c r="AA8">
+        <v>25</v>
+      </c>
+      <c r="AB8">
+        <v>64</v>
+      </c>
+      <c r="AC8">
+        <v>44</v>
+      </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>tech_pot!A9</f>
         <v>Bethisy-St-Pierre</v>
       </c>
+      <c r="B9">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>21</v>
+      </c>
+      <c r="D9">
+        <v>17</v>
+      </c>
+      <c r="E9">
+        <v>15</v>
+      </c>
+      <c r="F9">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>31</v>
+      </c>
+      <c r="M9">
+        <v>27</v>
+      </c>
+      <c r="N9">
+        <v>29</v>
+      </c>
+      <c r="O9">
+        <v>29</v>
+      </c>
+      <c r="P9">
+        <v>16</v>
+      </c>
+      <c r="Q9">
+        <v>22</v>
+      </c>
+      <c r="R9">
+        <v>23</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>14</v>
+      </c>
+      <c r="U9">
+        <v>3</v>
+      </c>
+      <c r="V9">
+        <v>6</v>
+      </c>
+      <c r="W9">
+        <v>7</v>
+      </c>
+      <c r="X9">
+        <v>21</v>
+      </c>
+      <c r="Y9">
+        <v>43</v>
+      </c>
+      <c r="Z9">
+        <v>26</v>
+      </c>
+      <c r="AA9">
+        <v>28</v>
+      </c>
+      <c r="AB9">
+        <v>57</v>
+      </c>
+      <c r="AC9">
+        <v>41</v>
+      </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>tech_pot!A10</f>
         <v>Bethisy-St-Martin</v>
       </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10">
+        <v>17</v>
+      </c>
+      <c r="F10">
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <v>14</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>30</v>
+      </c>
+      <c r="M10">
+        <v>26</v>
+      </c>
+      <c r="N10">
+        <v>28</v>
+      </c>
+      <c r="O10">
+        <v>28</v>
+      </c>
+      <c r="P10">
+        <v>17</v>
+      </c>
+      <c r="Q10">
+        <v>23</v>
+      </c>
+      <c r="R10">
+        <v>22</v>
+      </c>
+      <c r="S10">
+        <v>5</v>
+      </c>
+      <c r="T10">
+        <v>13</v>
+      </c>
+      <c r="U10">
+        <v>5</v>
+      </c>
+      <c r="V10">
+        <v>7</v>
+      </c>
+      <c r="W10">
+        <v>8</v>
+      </c>
+      <c r="X10">
+        <v>20</v>
+      </c>
+      <c r="Y10">
+        <v>51</v>
+      </c>
+      <c r="Z10">
+        <v>39</v>
+      </c>
+      <c r="AA10">
+        <v>41</v>
+      </c>
+      <c r="AB10">
+        <v>57</v>
+      </c>
+      <c r="AC10">
+        <v>42</v>
+      </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f>tech_pot!A11</f>
         <v>Bienville</v>
       </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>13</v>
+      </c>
+      <c r="F11">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>16</v>
+      </c>
+      <c r="H11">
+        <v>17</v>
+      </c>
+      <c r="I11">
+        <v>22</v>
+      </c>
+      <c r="J11">
+        <v>31</v>
+      </c>
+      <c r="K11">
+        <v>30</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>5</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11">
+        <v>5</v>
+      </c>
+      <c r="P11">
+        <v>14</v>
+      </c>
+      <c r="Q11">
+        <v>10</v>
+      </c>
+      <c r="R11">
+        <v>4</v>
+      </c>
+      <c r="S11">
+        <v>27</v>
+      </c>
+      <c r="T11">
+        <v>18</v>
+      </c>
+      <c r="U11">
+        <v>23</v>
+      </c>
+      <c r="V11">
+        <v>25</v>
+      </c>
+      <c r="W11">
+        <v>26</v>
+      </c>
+      <c r="X11">
+        <v>14</v>
+      </c>
+      <c r="Y11">
+        <v>27</v>
+      </c>
+      <c r="Z11">
+        <v>9</v>
+      </c>
+      <c r="AA11">
+        <v>9</v>
+      </c>
+      <c r="AB11">
+        <v>51</v>
+      </c>
+      <c r="AC11">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f>tech_pot!A12</f>
         <v>Choisy-au-Bac</v>
       </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>16</v>
+      </c>
+      <c r="H12">
+        <v>15</v>
+      </c>
+      <c r="I12">
+        <v>26</v>
+      </c>
+      <c r="J12">
+        <v>27</v>
+      </c>
+      <c r="K12">
+        <v>26</v>
+      </c>
+      <c r="L12">
+        <v>5</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12">
+        <v>14</v>
+      </c>
+      <c r="Q12">
+        <v>15</v>
+      </c>
+      <c r="R12">
+        <v>5</v>
+      </c>
+      <c r="S12">
+        <v>27</v>
+      </c>
+      <c r="T12">
+        <v>14</v>
+      </c>
+      <c r="U12">
+        <v>23</v>
+      </c>
+      <c r="V12">
+        <v>23</v>
+      </c>
+      <c r="W12">
+        <v>26</v>
+      </c>
+      <c r="X12">
+        <v>9</v>
+      </c>
+      <c r="Y12">
+        <v>19</v>
+      </c>
+      <c r="Z12">
+        <v>14</v>
+      </c>
+      <c r="AA12">
+        <v>17</v>
+      </c>
+      <c r="AB12">
+        <v>47</v>
+      </c>
+      <c r="AC12">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>tech_pot!A13</f>
         <v>Clairoix</v>
       </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>7</v>
+      </c>
+      <c r="E13">
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>14</v>
+      </c>
+      <c r="H13">
+        <v>15</v>
+      </c>
+      <c r="I13">
+        <v>20</v>
+      </c>
+      <c r="J13">
+        <v>29</v>
+      </c>
+      <c r="K13">
+        <v>28</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>3</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13">
+        <v>3</v>
+      </c>
+      <c r="P13">
+        <v>12</v>
+      </c>
+      <c r="Q13">
+        <v>13</v>
+      </c>
+      <c r="R13">
+        <v>3</v>
+      </c>
+      <c r="S13">
+        <v>25</v>
+      </c>
+      <c r="T13">
+        <v>16</v>
+      </c>
+      <c r="U13">
+        <v>21</v>
+      </c>
+      <c r="V13">
+        <v>23</v>
+      </c>
+      <c r="W13">
+        <v>24</v>
+      </c>
+      <c r="X13">
+        <v>12</v>
+      </c>
+      <c r="Y13">
+        <v>25</v>
+      </c>
+      <c r="Z13">
+        <v>12</v>
+      </c>
+      <c r="AA13">
+        <v>10</v>
+      </c>
+      <c r="AB13">
+        <v>49</v>
+      </c>
+      <c r="AC13">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f>tech_pot!A14</f>
         <v>Janville</v>
       </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>9</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>16</v>
+      </c>
+      <c r="H14">
+        <v>17</v>
+      </c>
+      <c r="I14">
+        <v>21</v>
+      </c>
+      <c r="J14">
+        <v>29</v>
+      </c>
+      <c r="K14">
+        <v>28</v>
+      </c>
+      <c r="L14">
+        <v>5</v>
+      </c>
+      <c r="M14">
+        <v>3</v>
+      </c>
+      <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>14</v>
+      </c>
+      <c r="Q14">
+        <v>15</v>
+      </c>
+      <c r="R14">
+        <v>5</v>
+      </c>
+      <c r="S14">
+        <v>27</v>
+      </c>
+      <c r="T14">
+        <v>16</v>
+      </c>
+      <c r="U14">
+        <v>23</v>
+      </c>
+      <c r="V14">
+        <v>25</v>
+      </c>
+      <c r="W14">
+        <v>26</v>
+      </c>
+      <c r="X14">
+        <v>12</v>
+      </c>
+      <c r="Y14">
+        <v>20</v>
+      </c>
+      <c r="Z14">
+        <v>14</v>
+      </c>
+      <c r="AA14">
+        <v>12</v>
+      </c>
+      <c r="AB14">
+        <v>49</v>
+      </c>
+      <c r="AC14">
+        <v>17</v>
+      </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f>tech_pot!A15</f>
         <v>Jonquières</v>
       </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>8</v>
+      </c>
+      <c r="I15">
+        <v>12</v>
+      </c>
+      <c r="J15">
+        <v>16</v>
+      </c>
+      <c r="K15">
+        <v>17</v>
+      </c>
+      <c r="L15">
+        <v>14</v>
+      </c>
+      <c r="M15">
+        <v>14</v>
+      </c>
+      <c r="N15">
+        <v>12</v>
+      </c>
+      <c r="O15">
+        <v>14</v>
+      </c>
+      <c r="P15">
+        <v>2</v>
+      </c>
+      <c r="Q15">
+        <v>7</v>
+      </c>
+      <c r="R15">
+        <v>9</v>
+      </c>
+      <c r="S15">
+        <v>17</v>
+      </c>
+      <c r="T15">
+        <v>20</v>
+      </c>
+      <c r="U15">
+        <v>14</v>
+      </c>
+      <c r="V15">
+        <v>16</v>
+      </c>
+      <c r="W15">
+        <v>14</v>
+      </c>
+      <c r="X15">
+        <v>22</v>
+      </c>
+      <c r="Y15">
+        <v>32</v>
+      </c>
+      <c r="Z15">
+        <v>11</v>
+      </c>
+      <c r="AA15">
+        <v>14</v>
+      </c>
+      <c r="AB15">
+        <v>59</v>
+      </c>
+      <c r="AC15">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f>tech_pot!A16</f>
         <v>Lachelle</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B16">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <v>18</v>
+      </c>
+      <c r="J16">
+        <v>22</v>
+      </c>
+      <c r="K16">
+        <v>23</v>
+      </c>
+      <c r="L16">
+        <v>10</v>
+      </c>
+      <c r="M16">
+        <v>15</v>
+      </c>
+      <c r="N16">
+        <v>13</v>
+      </c>
+      <c r="O16">
+        <v>15</v>
+      </c>
+      <c r="P16">
+        <v>7</v>
+      </c>
+      <c r="Q16">
+        <v>2</v>
+      </c>
+      <c r="R16">
+        <v>9</v>
+      </c>
+      <c r="S16">
+        <v>24</v>
+      </c>
+      <c r="T16">
+        <v>22</v>
+      </c>
+      <c r="U16">
+        <v>20</v>
+      </c>
+      <c r="V16">
+        <v>22</v>
+      </c>
+      <c r="W16">
+        <v>24</v>
+      </c>
+      <c r="X16">
+        <v>23</v>
+      </c>
+      <c r="Y16">
+        <v>33</v>
+      </c>
+      <c r="Z16">
+        <v>4</v>
+      </c>
+      <c r="AA16">
+        <v>7</v>
+      </c>
+      <c r="AB16">
+        <v>60</v>
+      </c>
+      <c r="AC16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f>tech_pot!A17</f>
         <v>Margny-lès-Compiègne</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+      <c r="F17">
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <v>11</v>
+      </c>
+      <c r="H17">
+        <v>11</v>
+      </c>
+      <c r="I17">
+        <v>16</v>
+      </c>
+      <c r="J17">
+        <v>23</v>
+      </c>
+      <c r="K17">
+        <v>22</v>
+      </c>
+      <c r="L17">
+        <v>4</v>
+      </c>
+      <c r="M17">
+        <v>5</v>
+      </c>
+      <c r="N17">
+        <v>3</v>
+      </c>
+      <c r="O17">
+        <v>5</v>
+      </c>
+      <c r="P17">
+        <v>9</v>
+      </c>
+      <c r="Q17">
+        <v>9</v>
+      </c>
+      <c r="R17">
+        <v>2</v>
+      </c>
+      <c r="S17">
+        <v>22</v>
+      </c>
+      <c r="T17">
+        <v>12</v>
+      </c>
+      <c r="U17">
+        <v>19</v>
+      </c>
+      <c r="V17">
+        <v>20</v>
+      </c>
+      <c r="W17">
+        <v>21</v>
+      </c>
+      <c r="X17">
+        <v>13</v>
+      </c>
+      <c r="Y17">
+        <v>27</v>
+      </c>
+      <c r="Z17">
+        <v>8</v>
+      </c>
+      <c r="AA17">
+        <v>11</v>
+      </c>
+      <c r="AB17">
+        <v>51</v>
+      </c>
+      <c r="AC17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f>tech_pot!A18</f>
         <v>Nery</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B18">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <v>19</v>
+      </c>
+      <c r="E18">
+        <v>17</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>14</v>
+      </c>
+      <c r="H18">
+        <v>10</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18">
+        <v>5</v>
+      </c>
+      <c r="L18">
+        <v>27</v>
+      </c>
+      <c r="M18">
+        <v>27</v>
+      </c>
+      <c r="N18">
+        <v>25</v>
+      </c>
+      <c r="O18">
+        <v>27</v>
+      </c>
+      <c r="P18">
+        <v>17</v>
+      </c>
+      <c r="Q18">
+        <v>24</v>
+      </c>
+      <c r="R18">
+        <v>22</v>
+      </c>
+      <c r="S18">
+        <v>2</v>
+      </c>
+      <c r="T18">
+        <v>19</v>
+      </c>
+      <c r="U18">
+        <v>5</v>
+      </c>
+      <c r="V18">
+        <v>7</v>
+      </c>
+      <c r="W18">
+        <v>10</v>
+      </c>
+      <c r="X18">
+        <v>25</v>
+      </c>
+      <c r="Y18">
+        <v>45</v>
+      </c>
+      <c r="Z18">
+        <v>27</v>
+      </c>
+      <c r="AA18">
+        <v>43</v>
+      </c>
+      <c r="AB18">
+        <v>66</v>
+      </c>
+      <c r="AC18">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f>tech_pot!A19</f>
         <v>Saint-Jean-aux-Bois</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <v>17</v>
+      </c>
+      <c r="E19">
+        <v>17</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>16</v>
+      </c>
+      <c r="H19">
+        <v>9</v>
+      </c>
+      <c r="I19">
+        <v>14</v>
+      </c>
+      <c r="J19">
+        <v>14</v>
+      </c>
+      <c r="K19">
+        <v>13</v>
+      </c>
+      <c r="L19">
+        <v>18</v>
+      </c>
+      <c r="M19">
+        <v>14</v>
+      </c>
+      <c r="N19">
+        <v>16</v>
+      </c>
+      <c r="O19">
+        <v>16</v>
+      </c>
+      <c r="P19">
+        <v>20</v>
+      </c>
+      <c r="Q19">
+        <v>22</v>
+      </c>
+      <c r="R19">
+        <v>12</v>
+      </c>
+      <c r="S19">
+        <v>19</v>
+      </c>
+      <c r="T19">
+        <v>2</v>
+      </c>
+      <c r="U19">
+        <v>15</v>
+      </c>
+      <c r="V19">
+        <v>17</v>
+      </c>
+      <c r="W19">
+        <v>16</v>
+      </c>
+      <c r="X19">
+        <v>7</v>
+      </c>
+      <c r="Y19">
+        <v>39</v>
+      </c>
+      <c r="Z19">
+        <v>27</v>
+      </c>
+      <c r="AA19">
+        <v>29</v>
+      </c>
+      <c r="AB19">
+        <v>50</v>
+      </c>
+      <c r="AC19">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f>tech_pot!A20</f>
         <v>Saintines</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>16</v>
+      </c>
+      <c r="D20">
+        <v>15</v>
+      </c>
+      <c r="E20">
+        <v>14</v>
+      </c>
+      <c r="F20">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>11</v>
+      </c>
+      <c r="H20">
+        <v>7</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <v>5</v>
+      </c>
+      <c r="L20">
+        <v>23</v>
+      </c>
+      <c r="M20">
+        <v>23</v>
+      </c>
+      <c r="N20">
+        <v>21</v>
+      </c>
+      <c r="O20">
+        <v>23</v>
+      </c>
+      <c r="P20">
+        <v>14</v>
+      </c>
+      <c r="Q20">
+        <v>20</v>
+      </c>
+      <c r="R20">
+        <v>19</v>
+      </c>
+      <c r="S20">
+        <v>5</v>
+      </c>
+      <c r="T20">
+        <v>15</v>
+      </c>
+      <c r="U20">
+        <v>2</v>
+      </c>
+      <c r="V20">
+        <v>3</v>
+      </c>
+      <c r="W20">
+        <v>4</v>
+      </c>
+      <c r="X20">
+        <v>22</v>
+      </c>
+      <c r="Y20">
+        <v>41</v>
+      </c>
+      <c r="Z20">
+        <v>24</v>
+      </c>
+      <c r="AA20">
+        <v>37</v>
+      </c>
+      <c r="AB20">
+        <v>61</v>
+      </c>
+      <c r="AC20">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f>tech_pot!A21</f>
         <v>Saint-Vaast de Longmont</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B21">
+        <v>18</v>
+      </c>
+      <c r="C21">
+        <v>18</v>
+      </c>
+      <c r="D21">
+        <v>17</v>
+      </c>
+      <c r="E21">
+        <v>14</v>
+      </c>
+      <c r="F21">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>8</v>
+      </c>
+      <c r="I21">
+        <v>4</v>
+      </c>
+      <c r="J21">
+        <v>6</v>
+      </c>
+      <c r="K21">
+        <v>7</v>
+      </c>
+      <c r="L21">
+        <v>25</v>
+      </c>
+      <c r="M21">
+        <v>23</v>
+      </c>
+      <c r="N21">
+        <v>23</v>
+      </c>
+      <c r="O21">
+        <v>25</v>
+      </c>
+      <c r="P21">
+        <v>16</v>
+      </c>
+      <c r="Q21">
+        <v>22</v>
+      </c>
+      <c r="R21">
+        <v>20</v>
+      </c>
+      <c r="S21">
+        <v>7</v>
+      </c>
+      <c r="T21">
+        <v>17</v>
+      </c>
+      <c r="U21">
+        <v>3</v>
+      </c>
+      <c r="V21">
+        <v>2</v>
+      </c>
+      <c r="W21">
+        <v>2</v>
+      </c>
+      <c r="X21">
+        <v>23</v>
+      </c>
+      <c r="Y21">
+        <v>43</v>
+      </c>
+      <c r="Z21">
+        <v>23</v>
+      </c>
+      <c r="AA21">
+        <v>36</v>
+      </c>
+      <c r="AB21">
+        <v>71</v>
+      </c>
+      <c r="AC21">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f>tech_pot!A22</f>
         <v>Verberie</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B22">
+        <v>16</v>
+      </c>
+      <c r="C22">
+        <v>16</v>
+      </c>
+      <c r="D22">
+        <v>18</v>
+      </c>
+      <c r="E22">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>11</v>
+      </c>
+      <c r="H22">
+        <v>7</v>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22">
+        <v>7</v>
+      </c>
+      <c r="K22">
+        <v>8</v>
+      </c>
+      <c r="L22">
+        <v>26</v>
+      </c>
+      <c r="M22">
+        <v>26</v>
+      </c>
+      <c r="N22">
+        <v>24</v>
+      </c>
+      <c r="O22">
+        <v>26</v>
+      </c>
+      <c r="P22">
+        <v>14</v>
+      </c>
+      <c r="Q22">
+        <v>24</v>
+      </c>
+      <c r="R22">
+        <v>21</v>
+      </c>
+      <c r="S22">
+        <v>10</v>
+      </c>
+      <c r="T22">
+        <v>16</v>
+      </c>
+      <c r="U22">
+        <v>4</v>
+      </c>
+      <c r="V22">
+        <v>2</v>
+      </c>
+      <c r="W22">
+        <v>2</v>
+      </c>
+      <c r="X22">
+        <v>22</v>
+      </c>
+      <c r="Y22">
+        <v>43</v>
+      </c>
+      <c r="Z22">
+        <v>21</v>
+      </c>
+      <c r="AA22">
+        <v>34</v>
+      </c>
+      <c r="AB22">
+        <v>70</v>
+      </c>
+      <c r="AC22">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f>tech_pot!A23</f>
         <v>Vieux-Moulin</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" t="str">
-        <f>tech_pot!A24</f>
-        <v>X</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" t="str">
-        <f>tech_pot!A25</f>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A26" t="str">
-        <f>tech_pot!A26</f>
-        <v>Z</v>
+      <c r="B23">
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <v>9</v>
+      </c>
+      <c r="D23">
+        <v>17</v>
+      </c>
+      <c r="E23">
+        <v>15</v>
+      </c>
+      <c r="F23">
+        <v>17</v>
+      </c>
+      <c r="G23">
+        <v>24</v>
+      </c>
+      <c r="H23">
+        <v>16</v>
+      </c>
+      <c r="I23">
+        <v>20</v>
+      </c>
+      <c r="J23">
+        <v>21</v>
+      </c>
+      <c r="K23">
+        <v>20</v>
+      </c>
+      <c r="L23">
+        <v>14</v>
+      </c>
+      <c r="M23">
+        <v>9</v>
+      </c>
+      <c r="N23">
+        <v>12</v>
+      </c>
+      <c r="O23">
+        <v>12</v>
+      </c>
+      <c r="P23">
+        <v>22</v>
+      </c>
+      <c r="Q23">
+        <v>23</v>
+      </c>
+      <c r="R23">
+        <v>13</v>
+      </c>
+      <c r="S23">
+        <v>25</v>
+      </c>
+      <c r="T23">
+        <v>7</v>
+      </c>
+      <c r="U23">
+        <v>22</v>
+      </c>
+      <c r="V23">
+        <v>23</v>
+      </c>
+      <c r="W23">
+        <v>22</v>
+      </c>
+      <c r="X23">
+        <v>2</v>
+      </c>
+      <c r="Y23">
+        <v>35</v>
+      </c>
+      <c r="Z23">
+        <v>22</v>
+      </c>
+      <c r="AA23">
+        <v>25</v>
+      </c>
+      <c r="AB23">
+        <v>45</v>
+      </c>
+      <c r="AC23">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24">
+        <v>28</v>
+      </c>
+      <c r="C24">
+        <v>28</v>
+      </c>
+      <c r="D24">
+        <v>27</v>
+      </c>
+      <c r="E24">
+        <v>30</v>
+      </c>
+      <c r="F24">
+        <v>33</v>
+      </c>
+      <c r="G24">
+        <v>34</v>
+      </c>
+      <c r="H24">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>39</v>
+      </c>
+      <c r="J24">
+        <v>43</v>
+      </c>
+      <c r="K24">
+        <v>51</v>
+      </c>
+      <c r="L24">
+        <v>27</v>
+      </c>
+      <c r="M24">
+        <v>19</v>
+      </c>
+      <c r="N24">
+        <v>25</v>
+      </c>
+      <c r="O24">
+        <v>20</v>
+      </c>
+      <c r="P24">
+        <v>32</v>
+      </c>
+      <c r="Q24">
+        <v>33</v>
+      </c>
+      <c r="R24">
+        <v>27</v>
+      </c>
+      <c r="S24">
+        <v>45</v>
+      </c>
+      <c r="T24">
+        <v>39</v>
+      </c>
+      <c r="U24">
+        <v>41</v>
+      </c>
+      <c r="V24">
+        <v>43</v>
+      </c>
+      <c r="W24">
+        <v>43</v>
+      </c>
+      <c r="X24">
+        <v>35</v>
+      </c>
+      <c r="Y24">
+        <v>2</v>
+      </c>
+      <c r="Z24">
+        <v>32</v>
+      </c>
+      <c r="AA24">
+        <v>25</v>
+      </c>
+      <c r="AB24">
+        <v>55</v>
+      </c>
+      <c r="AC24">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25">
+        <v>10</v>
+      </c>
+      <c r="D25">
+        <v>9</v>
+      </c>
+      <c r="E25">
+        <v>13</v>
+      </c>
+      <c r="F25">
+        <v>14</v>
+      </c>
+      <c r="G25">
+        <v>14</v>
+      </c>
+      <c r="H25">
+        <v>18</v>
+      </c>
+      <c r="I25">
+        <v>22</v>
+      </c>
+      <c r="J25">
+        <v>26</v>
+      </c>
+      <c r="K25">
+        <v>39</v>
+      </c>
+      <c r="L25">
+        <v>9</v>
+      </c>
+      <c r="M25">
+        <v>14</v>
+      </c>
+      <c r="N25">
+        <v>12</v>
+      </c>
+      <c r="O25">
+        <v>14</v>
+      </c>
+      <c r="P25">
+        <v>11</v>
+      </c>
+      <c r="Q25">
+        <v>4</v>
+      </c>
+      <c r="R25">
+        <v>8</v>
+      </c>
+      <c r="S25">
+        <v>27</v>
+      </c>
+      <c r="T25">
+        <v>27</v>
+      </c>
+      <c r="U25">
+        <v>24</v>
+      </c>
+      <c r="V25">
+        <v>23</v>
+      </c>
+      <c r="W25">
+        <v>21</v>
+      </c>
+      <c r="X25">
+        <v>22</v>
+      </c>
+      <c r="Y25">
+        <v>32</v>
+      </c>
+      <c r="Z25">
+        <v>2</v>
+      </c>
+      <c r="AA25">
+        <v>3</v>
+      </c>
+      <c r="AB25">
+        <v>60</v>
+      </c>
+      <c r="AC25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26">
+        <v>12</v>
+      </c>
+      <c r="C26">
+        <v>12</v>
+      </c>
+      <c r="D26">
+        <v>12</v>
+      </c>
+      <c r="E26">
+        <v>15</v>
+      </c>
+      <c r="F26">
+        <v>17</v>
+      </c>
+      <c r="G26">
+        <v>20</v>
+      </c>
+      <c r="H26">
+        <v>20</v>
+      </c>
+      <c r="I26">
+        <v>25</v>
+      </c>
+      <c r="J26">
+        <v>28</v>
+      </c>
+      <c r="K26">
+        <v>41</v>
+      </c>
+      <c r="L26">
+        <v>9</v>
+      </c>
+      <c r="M26">
+        <v>17</v>
+      </c>
+      <c r="N26">
+        <v>10</v>
+      </c>
+      <c r="O26">
+        <v>12</v>
+      </c>
+      <c r="P26">
+        <v>14</v>
+      </c>
+      <c r="Q26">
+        <v>7</v>
+      </c>
+      <c r="R26">
+        <v>11</v>
+      </c>
+      <c r="S26">
+        <v>43</v>
+      </c>
+      <c r="T26">
+        <v>29</v>
+      </c>
+      <c r="U26">
+        <v>37</v>
+      </c>
+      <c r="V26">
+        <v>36</v>
+      </c>
+      <c r="W26">
+        <v>34</v>
+      </c>
+      <c r="X26">
+        <v>25</v>
+      </c>
+      <c r="Y26">
+        <v>25</v>
+      </c>
+      <c r="Z26">
+        <v>3</v>
+      </c>
+      <c r="AA26">
+        <v>2</v>
+      </c>
+      <c r="AB26">
+        <v>63</v>
+      </c>
+      <c r="AC26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27">
+        <v>50</v>
+      </c>
+      <c r="C27">
+        <v>50</v>
+      </c>
+      <c r="D27">
+        <v>54</v>
+      </c>
+      <c r="E27">
+        <v>58</v>
+      </c>
+      <c r="F27">
+        <v>60</v>
+      </c>
+      <c r="G27">
+        <v>62</v>
+      </c>
+      <c r="H27">
+        <v>64</v>
+      </c>
+      <c r="I27">
+        <v>64</v>
+      </c>
+      <c r="J27">
+        <v>57</v>
+      </c>
+      <c r="K27">
+        <v>57</v>
+      </c>
+      <c r="L27">
+        <v>51</v>
+      </c>
+      <c r="M27">
+        <v>47</v>
+      </c>
+      <c r="N27">
+        <v>49</v>
+      </c>
+      <c r="O27">
+        <v>49</v>
+      </c>
+      <c r="P27">
+        <v>59</v>
+      </c>
+      <c r="Q27">
+        <v>60</v>
+      </c>
+      <c r="R27">
+        <v>51</v>
+      </c>
+      <c r="S27">
+        <v>66</v>
+      </c>
+      <c r="T27">
+        <v>50</v>
+      </c>
+      <c r="U27">
+        <v>61</v>
+      </c>
+      <c r="V27">
+        <v>71</v>
+      </c>
+      <c r="W27">
+        <v>70</v>
+      </c>
+      <c r="X27">
+        <v>45</v>
+      </c>
+      <c r="Y27">
+        <v>55</v>
+      </c>
+      <c r="Z27">
+        <v>60</v>
+      </c>
+      <c r="AA27">
+        <v>63</v>
+      </c>
+      <c r="AB27">
+        <v>2</v>
+      </c>
+      <c r="AC27">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28">
+        <v>18</v>
+      </c>
+      <c r="C28">
+        <v>18</v>
+      </c>
+      <c r="D28">
+        <v>17</v>
+      </c>
+      <c r="E28">
+        <v>28</v>
+      </c>
+      <c r="F28">
+        <v>30</v>
+      </c>
+      <c r="G28">
+        <v>30</v>
+      </c>
+      <c r="H28">
+        <v>26</v>
+      </c>
+      <c r="I28">
+        <v>44</v>
+      </c>
+      <c r="J28">
+        <v>41</v>
+      </c>
+      <c r="K28">
+        <v>42</v>
+      </c>
+      <c r="L28">
+        <v>13</v>
+      </c>
+      <c r="M28">
+        <v>17</v>
+      </c>
+      <c r="N28">
+        <v>15</v>
+      </c>
+      <c r="O28">
+        <v>17</v>
+      </c>
+      <c r="P28">
+        <v>27</v>
+      </c>
+      <c r="Q28">
+        <v>13</v>
+      </c>
+      <c r="R28">
+        <v>16</v>
+      </c>
+      <c r="S28">
+        <v>44</v>
+      </c>
+      <c r="T28">
+        <v>31</v>
+      </c>
+      <c r="U28">
+        <v>39</v>
+      </c>
+      <c r="V28">
+        <v>37</v>
+      </c>
+      <c r="W28">
+        <v>35</v>
+      </c>
+      <c r="X28">
+        <v>26</v>
+      </c>
+      <c r="Y28">
+        <v>19</v>
+      </c>
+      <c r="Z28">
+        <v>9</v>
+      </c>
+      <c r="AA28">
+        <v>6</v>
+      </c>
+      <c r="AB28">
+        <v>64</v>
+      </c>
+      <c r="AC28">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2775,6 +6024,239 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EC2AB40-5CA3-462E-A87B-9CF9631CDA94}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="str">
+        <f>mun!A2</f>
+        <v>Compiègne</v>
+      </c>
+      <c r="B2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="str">
+        <f>mun!A3</f>
+        <v>Venette</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="str">
+        <f>mun!A4</f>
+        <v>Jaux</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="str">
+        <f>mun!A5</f>
+        <v>Armancourt</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="str">
+        <f>mun!A6</f>
+        <v>Le Meux</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="str">
+        <f>mun!A7</f>
+        <v>La Croix-St-Ouen</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="str">
+        <f>mun!A8</f>
+        <v>St-Sauveur</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="str">
+        <f>mun!A9</f>
+        <v>Bethisy-St-Pierre</v>
+      </c>
+      <c r="B9">
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="str">
+        <f>mun!A10</f>
+        <v>Bethisy-St-Martin</v>
+      </c>
+      <c r="B10">
+        <v>19</v>
+      </c>
+      <c r="C10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="str">
+        <f>mun!A11</f>
+        <v>Bienville</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="str">
+        <f>mun!A12</f>
+        <v>Choisy-au-Bac</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="str">
+        <f>mun!A13</f>
+        <v>Clairoix</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="str">
+        <f>mun!A14</f>
+        <v>Janville</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="str">
+        <f>mun!A15</f>
+        <v>Jonquières</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="str">
+        <f>mun!A16</f>
+        <v>Lachelle</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="str">
+        <f>mun!A17</f>
+        <v>Margny-lès-Compiègne</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="str">
+        <f>mun!A18</f>
+        <v>Nery</v>
+      </c>
+      <c r="B18">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="str">
+        <f>mun!A19</f>
+        <v>Saint-Jean-aux-Bois</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="str">
+        <f>mun!A20</f>
+        <v>Saintines</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="str">
+        <f>mun!A21</f>
+        <v>Saint-Vaast de Longmont</v>
+      </c>
+      <c r="B21">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="str">
+        <f>mun!A22</f>
+        <v>Verberie</v>
+      </c>
+      <c r="B22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="str">
+        <f>mun!A23</f>
+        <v>Vieux-Moulin</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{992B2B0E-AECF-41DB-AC20-A757648DB06D}">
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2798,28 +6280,28 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
       <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
       <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
       <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
         <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -2977,7 +6459,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
